--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rc62df00c40b7461d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R782be1d9d8c147ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Rc905faf5614b4598"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R85e37ba523074562"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Ref803d3f206844f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R0eb9709dbc9e40da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R51b89599006f460d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Rf5ce0917d9394a5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rea67a5a791744dff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rc31281bd8c6041db"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -382,16 +382,30 @@
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="6" t="str">
+      <x:c r="A8" s="5" t="str">
+        <x:v>窗口交接</x:v>
+      </x:c>
+      <x:c r="B8" s="5" t="str">
+        <x:v>output/results/release_handoff.csv</x:v>
+      </x:c>
+      <x:c r="C8" s="5" t="str">
+        <x:v>记录发布安排与回退条件</x:v>
+      </x:c>
+      <x:c r="D8" s="5" t="str">
+        <x:v>与release_request.json核对</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="6" t="str">
         <x:v>岗位说明</x:v>
       </x:c>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="B9" s="6" t="str">
         <x:v>output/README.txt</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>说明材料消费者和维护窗职责</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>与变更说明互证</x:v>
       </x:c>
     </x:row>
@@ -485,7 +499,7 @@
         <x:v>feature_snapshot.wait_for_traffic</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>external_task_id</x:v>
+        <x:v>上游任务</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
         <x:v>finalize_partition</x:v>
@@ -513,7 +527,7 @@
         <x:v>ranker_release.wait_for_features</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
-        <x:v>external_task_id</x:v>
+        <x:v>上游任务</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
         <x:v>publish_snapshot</x:v>
@@ -537,17 +551,59 @@
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="6" t="str">
+      <x:c r="A10" s="5" t="str">
         <x:v>全部DAG</x:v>
       </x:c>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="B10" s="5" t="str">
         <x:v>catchup</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C10" s="5" t="str">
         <x:v>true</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D10" s="5" t="str">
         <x:v>DagBag</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="5" t="str">
+        <x:v>release_handoff</x:v>
+      </x:c>
+      <x:c r="B11" s="5" t="str">
+        <x:v>release_window</x:v>
+      </x:c>
+      <x:c r="C11" s="5" t="str">
+        <x:v>2026-04-22T01:00:00Z/2026-04-22T02:00:00Z</x:v>
+      </x:c>
+      <x:c r="D11" s="5" t="str">
+        <x:v>release_request.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="5" t="str">
+        <x:v>release_handoff</x:v>
+      </x:c>
+      <x:c r="B12" s="5" t="str">
+        <x:v>rollout_mode</x:v>
+      </x:c>
+      <x:c r="C12" s="5" t="str">
+        <x:v>paused_schedule_then_activate</x:v>
+      </x:c>
+      <x:c r="D12" s="5" t="str">
+        <x:v>release_request.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="6" t="str">
+        <x:v>release_handoff</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
+        <x:v>rollback_condition</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="str">
+        <x:v>dag_import_error_or_sensor_timeout</x:v>
+      </x:c>
+      <x:c r="D13" s="6" t="str">
+        <x:v>release_request.json</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -643,7 +699,7 @@
         <x:v>文件</x:v>
       </x:c>
       <x:c r="C6" s="6" t="str">
-        <x:v>dag_inventory.csv、dependency_inventory.csv、release_sequence.csv</x:v>
+        <x:v>dag_inventory.csv、dependency_inventory.csv、release_sequence.csv、release_handoff.csv</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
         <x:v>文件集合精确匹配</x:v>
@@ -785,37 +841,20 @@
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="5" t="str">
-        <x:v>release_sequence</x:v>
-      </x:c>
-      <x:c r="B8" s="5" t="str">
-        <x:v>feature_snapshot上游逻辑时间</x:v>
-      </x:c>
-      <x:c r="C8" s="5" t="n">
-        <x:v>46132</x:v>
-      </x:c>
-      <x:c r="D8" s="5" t="n">
+      <x:c r="A8" s="6" t="str">
+        <x:v>release_handoff</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>wait_budget_seconds</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E8" s="5" t="str">
-        <x:v>参考日期与偏移</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="6" t="str">
-        <x:v>release_sequence</x:v>
-      </x:c>
-      <x:c r="B9" s="6" t="str">
-        <x:v>ranker_release上游逻辑时间</x:v>
-      </x:c>
-      <x:c r="C9" s="6" t="n">
-        <x:v>46132.083333333336</x:v>
-      </x:c>
-      <x:c r="D9" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>参考日期与偏移</x:v>
+      <x:c r="E8" s="6" t="str">
+        <x:v>release_request.json</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
